--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04943F6-6C7E-46DF-BCCB-B97D68EEF871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -12,19 +18,20 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
+    <sheet name="Tabla_590166" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_14">Hidden_1!$A$1:$A$7</definedName>
+    <definedName name="Hidden_14">Hidden_1!$A$1:$A$8</definedName>
     <definedName name="Hidden_29">Hidden_2!$A$1:$A$3</definedName>
-    <definedName name="Hidden_314">Hidden_3!$A$1:$A$2</definedName>
-    <definedName name="Hidden_424">Hidden_4!$A$1:$A$2</definedName>
+    <definedName name="Hidden_313">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_425">Hidden_4!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="105">
   <si>
     <t>48981</t>
   </si>
@@ -56,6 +63,9 @@
     <t>2</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -104,10 +114,13 @@
     <t>436375</t>
   </si>
   <si>
+    <t>571934</t>
+  </si>
+  <si>
     <t>436376</t>
   </si>
   <si>
-    <t>571934</t>
+    <t>590166</t>
   </si>
   <si>
     <t>436382</t>
@@ -146,9 +159,6 @@
     <t>436369</t>
   </si>
   <si>
-    <t>436384</t>
-  </si>
-  <si>
     <t>436389</t>
   </si>
   <si>
@@ -185,21 +195,25 @@
     <t>Sector al cual se otorgó el acto jurídico (catálogo)</t>
   </si>
   <si>
-    <t>Nombre(s) del titular al cual se otorgó el acto jurídico</t>
-  </si>
-  <si>
-    <t>Primer apellido del titular al cual se otorgó el acto jurídico</t>
-  </si>
-  <si>
-    <t>Segundo apellido del titular al cual se otorgó el acto jurídico</t>
-  </si>
-  <si>
-    <t>Razón social del titular al cual se otorgó el acto jurídico</t>
+    <t>Nombre(s) de la persona física titular a quien se otorgó el acto jurídico</t>
+  </si>
+  <si>
+    <t>Primer apellido de la persona física titular a quien se otorgó el acto jurídico</t>
+  </si>
+  <si>
+    <t>Segundo apellido de la persona física titular a quien se otorgó el acto jurídico</t>
   </si>
   <si>
     <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
   </si>
   <si>
+    <t>Razón social de la persona moral titular a quien se otorgó el acto jurídico</t>
+  </si>
+  <si>
+    <t>Persona(s) beneficiaria(s) final(es) 
+Tabla_590166</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fecha de inicio de vigencia del acto jurídico </t>
   </si>
   <si>
@@ -236,16 +250,13 @@
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
   </si>
   <si>
     <t/>
@@ -254,19 +265,22 @@
     <t>Departamento  de Recursos Humanos</t>
   </si>
   <si>
-    <t>46B74D34241333EAF68B963D189D8D89</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>14/07/2023</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
+    <t>DC97447CC5565FC244F93F7F6035A12B</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>14568082</t>
+  </si>
+  <si>
+    <t>12/04/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de enero de 2024 al 31 de marzo de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
   </si>
   <si>
     <t>Licencia</t>
@@ -290,6 +304,9 @@
     <t>Asignaciones</t>
   </si>
   <si>
+    <t>Otro (especificar)</t>
+  </si>
+  <si>
     <t>Privado</t>
   </si>
   <si>
@@ -309,12 +326,33 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>81235</t>
+  </si>
+  <si>
+    <t>81237</t>
+  </si>
+  <si>
+    <t>81236</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Nombre(s) de la persona beneficiaria final</t>
+  </si>
+  <si>
+    <t>Primer apellido de la persona beneficiaria final</t>
+  </si>
+  <si>
+    <t>Segundo apellido de la persona beneficiaria final</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -385,8 +423,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -394,7 +435,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -409,6 +450,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -425,44 +469,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -490,14 +534,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -525,6 +586,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -536,175 +614,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -714,24 +768,24 @@
     <col min="8" max="8" width="46.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="47.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="49.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="51.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="55.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="49.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="65.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="38" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="77.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="69.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="49.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="255" bestFit="1" customWidth="1"/>
   </cols>
@@ -742,36 +796,36 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -811,359 +865,359 @@
         <v>6</v>
       </c>
       <c r="N4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
         <v>6</v>
       </c>
-      <c r="O4" t="s">
-        <v>8</v>
-      </c>
       <c r="P4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="s">
         <v>7</v>
       </c>
       <c r="R4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" t="s">
         <v>6</v>
       </c>
-      <c r="S4" t="s">
-        <v>10</v>
-      </c>
       <c r="T4" t="s">
+        <v>11</v>
+      </c>
+      <c r="U4" t="s">
         <v>9</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
+        <v>12</v>
+      </c>
+      <c r="W4" t="s">
         <v>11</v>
       </c>
-      <c r="V4" t="s">
-        <v>10</v>
-      </c>
-      <c r="W4" t="s">
-        <v>10</v>
-      </c>
       <c r="X4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
         <v>8</v>
       </c>
-      <c r="Z4" t="s">
-        <v>10</v>
-      </c>
       <c r="AA4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB4" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" t="s">
-        <v>7</v>
-      </c>
       <c r="AC4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Z5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AC5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
-      <c r="AB6" s="4"/>
-      <c r="AC6" s="4"/>
-      <c r="AD6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
     </row>
     <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="I7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="M7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="N7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="O7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="P7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="Q7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="R7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="S7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="T7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="U7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="V7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="W7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="X7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="Y7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="Z7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AA7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AB7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AC7" s="2" t="s">
         <v>72</v>
       </c>
+      <c r="AD7" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>80</v>
+      <c r="AC8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1177,17 +1231,17 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J199" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O200">
-      <formula1>Hidden_314</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N199" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>Hidden_313</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y200">
-      <formula1>Hidden_424</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z199" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>Hidden_425</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1195,43 +1249,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1240,23 +1299,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1265,18 +1324,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1285,18 +1344,70 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVII/LTAIPT_A63F27.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04943F6-6C7E-46DF-BCCB-B97D68EEF871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D501B797-B542-4C5F-9E32-0C12C045A1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,31 +256,31 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>E8EFB9FD7024A91B4AA09AAE1854377C</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>16084491</t>
+  </si>
+  <si>
     <t>Departamento  de Recursos Humanos</t>
   </si>
   <si>
-    <t>DC97447CC5565FC244F93F7F6035A12B</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>14568082</t>
-  </si>
-  <si>
-    <t>12/04/2024</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2024 al 31 de marzo de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
+    <t>18/10/2024</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2024 al 30 de septiembre de 2024, el Colegio de Bachilleres del Estado de Tlaxcala no realiza consesiones para ejecución y operación de obra pública,prestación de servicio público , radiodifusión, telcomuniaciones;  no otorga permisos para el tratamiento y refinación del petroleo, almacenamiento, transporte y distribución  de ductos de petróleo, gas, petroliferos y petroquimicos; de radiodifución  de telecomunicación, de ocnducir; no otorga licencias de uso de suelo, de construcción, de anuncios, de conducir, de explotación de yacimientos de materiales pétreos, de explotación  y exracción del petróleo; no autoriza cambios de giro de locales del mercadopúblico, de espectáculos en la vía pública, parques o espacios públicos, de usos y ocupación, del Programa especial de protección civil , de juegos pirotécnicos; para impartir educación, para el accesoa la multiprogramación;  no realiza contratos con cargo total o parcial a recursos públicos; no realiza convenios  para desarrollar un asunto concreo destinado a establecer, transferir, modificar o eliminar  una obligació; debido a que dichos actos jurídicos no se encuentran dentro de sus atribuciones establecidas por ser una Institución Educativa, la cual tiene por objeto, en la esfera de su competencia estatal, impartir, impulsar, coordinar y normar la educación correspondiente al ciclo de nivel medio superior, lo anterior establecido en su Reglamento Interior vigente.</t>
   </si>
   <si>
     <t>Licencia</t>
@@ -1130,88 +1130,88 @@
     </row>
     <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>81</v>
@@ -1231,16 +1231,16 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E196" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J199" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J196" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N199" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N196" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_313</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z199" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z196" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>Hidden_425</formula1>
     </dataValidation>
   </dataValidations>
